--- a/data/review/gpt-5.4-pro/tiebreak/step-3-tiebreak.xlsx
+++ b/data/review/gpt-5.4-pro/tiebreak/step-3-tiebreak.xlsx
@@ -417,13 +417,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="90" customWidth="1" min="2" max="2"/>
     <col width="40" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -447,6 +448,11 @@
           <t>decision</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Reviewer</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="0"/>
